--- a/resources/templates/standard/A4100-05.xlsx
+++ b/resources/templates/standard/A4100-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>양식 제,개정 신청서</t>
   </si>
@@ -687,12 +690,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -707,25 +712,25 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
@@ -796,7 +801,7 @@
     </row>
     <row r="4" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -808,7 +813,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
@@ -820,7 +825,7 @@
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
@@ -834,7 +839,7 @@
     </row>
     <row r="5" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -871,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -905,7 +910,7 @@
     <row r="7" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1005,7 +1010,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -1039,7 +1044,7 @@
     <row r="11" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1139,7 +1144,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1173,7 +1178,7 @@
     <row r="15" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1273,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -1307,7 +1312,7 @@
     <row r="19" ht="17.45" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1404,7 +1409,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1438,7 +1443,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -1449,7 +1454,7 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
@@ -1466,19 +1471,19 @@
       <c r="W23" s="14"/>
       <c r="X23" s="14"/>
       <c r="Y23" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z23" s="12"/>
       <c r="AA23" s="12"/>
       <c r="AB23" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC23" s="12"/>
       <c r="AD23" s="12"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
@@ -1512,7 +1517,7 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1546,7 +1551,7 @@
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -1557,7 +1562,7 @@
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="J26" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
@@ -1574,19 +1579,19 @@
       <c r="W26" s="19"/>
       <c r="X26" s="19"/>
       <c r="Y26" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z26" s="20"/>
       <c r="AA26" s="20"/>
       <c r="AB26" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC26" s="20"/>
       <c r="AD26" s="20"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1620,7 +1625,7 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -1654,7 +1659,7 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -1665,7 +1670,7 @@
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -1682,19 +1687,19 @@
       <c r="W29" s="24"/>
       <c r="X29" s="24"/>
       <c r="Y29" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z29" s="25"/>
       <c r="AA29" s="25"/>
       <c r="AB29" s="25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC29" s="25"/>
       <c r="AD29" s="25"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1728,7 +1733,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -1762,7 +1767,7 @@
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -1773,7 +1778,7 @@
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
       <c r="J32" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="19"/>
       <c r="L32" s="19"/>
@@ -1790,19 +1795,19 @@
       <c r="W32" s="19"/>
       <c r="X32" s="19"/>
       <c r="Y32" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z32" s="20"/>
       <c r="AA32" s="20"/>
       <c r="AB32" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC32" s="20"/>
       <c r="AD32" s="20"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -1836,7 +1841,7 @@
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="26"/>
@@ -1870,7 +1875,7 @@
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1904,7 +1909,7 @@
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -1915,7 +1920,7 @@
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
@@ -1932,19 +1937,19 @@
       <c r="W36" s="14"/>
       <c r="X36" s="14"/>
       <c r="Y36" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z36" s="12"/>
       <c r="AA36" s="12"/>
       <c r="AB36" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC36" s="12"/>
       <c r="AD36" s="12"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -1978,7 +1983,7 @@
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -2012,13 +2017,13 @@
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
